--- a/output/casestudy_20260824.xlsx
+++ b/output/casestudy_20260824.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>13.57419890002348</v>
+        <v>10.85729750001337</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11.32227909995709</v>
+        <v>10.81438070000149</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>11.56995979999192</v>
+        <v>11.08797190000769</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>12.04047480004374</v>
+        <v>11.1877471000189</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>12.22845470008906</v>
+        <v>11.30869330000132</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>12.14157659991179</v>
+        <v>11.30121659999713</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13.6 초</t>
+          <t>10.9 초</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.3 초</t>
+          <t>10.8 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11.6 초</t>
+          <t>11.1 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.0 초</t>
+          <t>11.2 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12.2 초</t>
+          <t>11.3 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12.1 초</t>
+          <t>11.3 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>75.0 초</t>
+          <t>68.3 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260824.xlsx
+++ b/output/casestudy_20260824.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.85729750001337</v>
+        <v>10.77083930000663</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10.81438070000149</v>
+        <v>10.66690479998942</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>11.08797190000769</v>
+        <v>10.98419220000505</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11.1877471000189</v>
+        <v>11.11672290007118</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11.30869330000132</v>
+        <v>11.24546330003068</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>11.30121659999713</v>
+        <v>11.27665990008973</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.9 초</t>
+          <t>10.8 초</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.8 초</t>
+          <t>10.7 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11.1 초</t>
+          <t>11.0 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.2 초</t>
+          <t>11.1 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.3 초</t>
+          <t>11.2 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>68.3 초</t>
+          <t>67.8 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260824.xlsx
+++ b/output/casestudy_20260824.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.77083930000663</v>
+        <v>10.86007120006252</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10.66690479998942</v>
+        <v>10.73995690001175</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>10.98419220000505</v>
+        <v>10.92912959994283</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11.11672290007118</v>
+        <v>11.16896349994931</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11.24546330003068</v>
+        <v>11.75658279994968</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>11.27665990008973</v>
+        <v>11.31830359995365</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.8 초</t>
+          <t>10.9 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11.0 초</t>
+          <t>10.9 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.1 초</t>
+          <t>11.2 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.2 초</t>
+          <t>11.8 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>67.8 초</t>
+          <t>68.6 초</t>
         </is>
       </c>
     </row>
